--- a/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
+++ b/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$2</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
@@ -418,12 +421,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -550,7 +568,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -562,34 +580,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -674,15 +692,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1040,13 +1062,25 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:5">
       <c r="A2" s="2"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E19 E1:E16 E20:E1048576">
+      <formula1>"每周,月度,季度,半年,年度,2.5年,5年"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"甲板部,机舱部"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576 H$1:H$1048576">
+      <formula1>"船长,大副,二副,三副,轮机长,二管轮,三管轮"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
+++ b/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
@@ -13,6 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$2</definedName>
+    <definedName name="甲板部">Sheet1!$F$7:$F$9</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -36,7 +37,7 @@
     <t>周期(只能填每周，月度，季度，半年，年度，2.5年，5年)</t>
   </si>
   <si>
-    <t>部门(甲板部或机舱部)</t>
+    <t>机舱部</t>
   </si>
   <si>
     <t>执行人</t>
@@ -1071,13 +1072,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E19 E1:E16 E20:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E$1:E$1048576">
       <formula1>"每周,月度,季度,半年,年度,2.5年,5年"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F$1:F$1048576">
       <formula1>"甲板部,机舱部"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576 H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G$1:G$1048576 H$1:H$1048576">
       <formula1>"船长,大副,二副,三副,轮机长,二管轮,三管轮"</formula1>
     </dataValidation>
   </dataValidations>

--- a/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
+++ b/WebHost/wwwroot/eam/basexlsx/维保项目导入模板.xlsx
@@ -12,20 +12,26 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$2</definedName>
-    <definedName name="甲板部">Sheet1!$F$7:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$2</definedName>
+    <definedName name="甲板部">Sheet1!$H$7:$H$9</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>序号</t>
   </si>
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>船舶编号</t>
+  </si>
+  <si>
+    <t>船舶名称</t>
   </si>
   <si>
     <t>维保项目</t>
@@ -37,7 +43,7 @@
     <t>周期(只能填每周，月度，季度，半年，年度，2.5年，5年)</t>
   </si>
   <si>
-    <t>机舱部</t>
+    <t>部门(甲板部或机舱部)</t>
   </si>
   <si>
     <t>执行人</t>
@@ -693,7 +699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,10 +708,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1018,20 +1020,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="3" max="3" width="35.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="32.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.4444444444444" customWidth="1"/>
-    <col min="8" max="8" width="11.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="16.5555555555556" customWidth="1"/>
-    <col min="10" max="10" width="55.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="29.1111111111111" customWidth="1"/>
+    <col min="4" max="5" width="35.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="32.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="11.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="11.2222222222222" customWidth="1"/>
+    <col min="11" max="11" width="16.5555555555556" customWidth="1"/>
+    <col min="12" max="12" width="55.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" spans="1:10">
+    <row r="1" ht="45" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,24 +1065,32 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:1">
       <c r="A2" s="2"/>
-      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="E$1:E$1048576">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G$1:G$1048576">
       <formula1>"每周,月度,季度,半年,年度,2.5年,5年"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H$1:H$1048576">
       <formula1>"甲板部,机舱部"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G$1:G$1048576 H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I$1:I$1048576 J$1:J$1048576">
       <formula1>"船长,大副,二副,三副,轮机长,二管轮,三管轮"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K$1:K$1048576">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
